--- a/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMPregnancyHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
